--- a/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
@@ -1,40 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_Evidence" sheetId="1" r:id="R70c6e56916b34c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_INDEX" sheetId="2" r:id="Rd99193d273104138"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="3" r:id="R8b6feb23e1894e76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_入力フロー" sheetId="4" r:id="R217a587c459e4788"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_取替方式" sheetId="5" r:id="Rf035899f4399451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02A_仕様区分" sheetId="6" r:id="R9deb1695f62144bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_窓種" sheetId="7" r:id="R638a068440dd48f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03A_枠仕様" sheetId="8" r:id="R091731448ce64e8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03B_窓種枠設定" sheetId="9" r:id="Rdd8aa67ed3794cc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_窓種固有仕様" sheetId="10" r:id="R56540359ff0043ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_サイズルール" sheetId="11" r:id="R883cf115be6d42e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05A_サイズ区間" sheetId="12" r:id="Ree16c238895e43c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05B_境界ルール" sheetId="13" r:id="R06eb2388d2e044d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_色" sheetId="14" r:id="R548dd4dac61b4914"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06A_色適用条件" sheetId="15" r:id="R5ea48338757b4af8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_網戸" sheetId="16" r:id="R4cda38aecfff4624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07A_網戸適用条件" sheetId="17" r:id="R79e0a32133c84045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_ガラス" sheetId="18" r:id="Rf5077606a3b24d2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08A_ガラス適用条件" sheetId="19" r:id="R7167c938463e45ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_その他OP" sheetId="20" r:id="R8d7e33acdb36431f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09A_OP依存関係" sheetId="21" r:id="Ra4e28a4cb0e14d40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_適用条件" sheetId="22" r:id="Re5716c4fd93c4679"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10A_既設窓互換" sheetId="23" r:id="R2750f7632b6540fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10B_現調項目" sheetId="24" r:id="Ref30eb655fdf4900"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_QA" sheetId="25" r:id="R54d39e2433344ab2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_開口構成" sheetId="26" r:id="Rbd7362f84694478f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_見積入力テスト" sheetId="27" r:id="R613e086e47ec4ed6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C_化粧カバー見付" sheetId="28" r:id="R9ed0cb77c0ea4b2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_共通参照" sheetId="29" r:id="Rdac8c77bbeee4d71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08B_地域条件" sheetId="30" r:id="R86bc85c272c2436f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09B_室内樹脂カバー" sheetId="31" r:id="R3bf407359da544ab"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="90_Evidence" sheetId="1" r:id="R70c6e56916b34c6d"/>
+    <sheet name="00_INDEX" sheetId="2" r:id="Rd99193d273104138"/>
+    <sheet name="00_README" sheetId="3" r:id="R8b6feb23e1894e76"/>
+    <sheet name="01_入力フロー" sheetId="4" r:id="R217a587c459e4788"/>
+    <sheet name="02_取替方式" sheetId="5" r:id="Rf035899f4399451f"/>
+    <sheet name="02A_仕様区分" sheetId="6" r:id="R9deb1695f62144bd"/>
+    <sheet name="03_窓種" sheetId="7" r:id="R638a068440dd48f9"/>
+    <sheet name="03A_枠仕様" sheetId="8" r:id="R091731448ce64e8b"/>
+    <sheet name="03B_窓種枠設定" sheetId="9" r:id="Rdd8aa67ed3794cc5"/>
+    <sheet name="04_窓種固有仕様" sheetId="10" r:id="R56540359ff0043ec"/>
+    <sheet name="05_サイズルール" sheetId="11" r:id="R883cf115be6d42e0"/>
+    <sheet name="05A_サイズ区間" sheetId="12" r:id="Ree16c238895e43c7"/>
+    <sheet name="05B_境界ルール" sheetId="13" r:id="R06eb2388d2e044d4"/>
+    <sheet name="06_色" sheetId="14" r:id="R548dd4dac61b4914"/>
+    <sheet name="06A_色適用条件" sheetId="15" r:id="R5ea48338757b4af8"/>
+    <sheet name="07_網戸" sheetId="16" r:id="R4cda38aecfff4624"/>
+    <sheet name="07A_網戸適用条件" sheetId="17" r:id="R79e0a32133c84045"/>
+    <sheet name="08_ガラス" sheetId="18" r:id="Rf5077606a3b24d2b"/>
+    <sheet name="08A_ガラス適用条件" sheetId="19" r:id="R7167c938463e45ec"/>
+    <sheet name="09_その他OP" sheetId="20" r:id="R8d7e33acdb36431f"/>
+    <sheet name="09A_OP依存関係" sheetId="21" r:id="Ra4e28a4cb0e14d40"/>
+    <sheet name="10_適用条件" sheetId="22" r:id="Re5716c4fd93c4679"/>
+    <sheet name="10A_既設窓互換" sheetId="23" r:id="R2750f7632b6540fa"/>
+    <sheet name="10B_現調項目" sheetId="24" r:id="Ref30eb655fdf4900"/>
+    <sheet name="99_QA" sheetId="25" r:id="R54d39e2433344ab2"/>
+    <sheet name="04A_開口構成" sheetId="26" r:id="Rbd7362f84694478f"/>
+    <sheet name="11_見積入力テスト" sheetId="27" r:id="R613e086e47ec4ed6"/>
+    <sheet name="10C_化粧カバー見付" sheetId="28" r:id="R9ed0cb77c0ea4b2a"/>
+    <sheet name="12_共通参照" sheetId="29" r:id="Rdac8c77bbeee4d71"/>
+    <sheet name="08B_地域条件" sheetId="30" r:id="R86bc85c272c2436f"/>
+    <sheet name="09B_室内樹脂カバー" sheetId="31" r:id="R3bf407359da544ab"/>
+    <sheet name="14_UI選択契約" sheetId="32" r:id="rIdReplusUiV9"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1453,6 +1454,643 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/replus-ui-v9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="251">
+        <v>リプラス住宅用・共通UI選択契約</v>
+      </c>
+      <c r="B1" s="252"/>
+      <c r="C1" s="252"/>
+      <c r="D1" s="252"/>
+      <c r="E1" s="253"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="str" s="248">
+        <v>分類</v>
+      </c>
+      <c r="B2" t="str" s="249">
+        <v>対象</v>
+      </c>
+      <c r="C2" t="str" s="249">
+        <v>依存元</v>
+      </c>
+      <c r="D2" t="str" s="249">
+        <v>処理</v>
+      </c>
+      <c r="E2" t="str" s="250">
+        <v>根拠区分</v>
+      </c>
+      <c r="F2" t="str">
+        <v>revision</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str" s="251">
+        <v>色連動</v>
+      </c>
+      <c r="B3" t="str" s="252">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C3" t="str" s="252">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="D3" t="str" s="252">
+        <v>{"targetField": "exterior_cover_color", "parents": ["sash_exterior_color"], "cases": [{"when": {"sash_exterior_color": "T"}, "value": "T"}, {"when": {"sash_exterior_color": "G"}, "value": "G"}, {"when": {"sash_exterior_color": "C"}, "value": "C"}, {"when": {"sash_exterior_color": "F"}, "value": "F"}], "resolvedMessage": "本体外観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E3" t="str" s="253">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F3" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str" s="251">
+        <v>色連動</v>
+      </c>
+      <c r="B4" t="str" s="252">
+        <v>interior_resin_cover_color</v>
+      </c>
+      <c r="C4" t="str" s="252">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="D4" t="str" s="252">
+        <v>{"targetField": "interior_resin_cover_color", "parents": ["sash_interior_color"], "cases": [{"when": {"sash_interior_color": "F"}, "value": "F"}], "resolvedMessage": "本体内観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E4" t="str" s="253">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F4" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B5" t="str" s="252">
+        <v>window_type</v>
+      </c>
+      <c r="C5" t="str" s="252"/>
+      <c r="D5" t="str" s="252">
+        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E5" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F5" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B6" t="str" s="252">
+        <v>frame_type</v>
+      </c>
+      <c r="C6" t="str" s="252">
+        <v>window_type</v>
+      </c>
+      <c r="D6" t="str" s="252">
+        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E6" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F6" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B7" t="str" s="252">
+        <v>spec_panel_configuration</v>
+      </c>
+      <c r="C7" t="str" s="252">
+        <v>window_type</v>
+      </c>
+      <c r="D7" t="str" s="252">
+        <v>{"label": "建数", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E7" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F7" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B8" t="str" s="252">
+        <v>spec_height_category</v>
+      </c>
+      <c r="C8" t="str" s="252">
+        <v>window_type,custom_width,custom_height</v>
+      </c>
+      <c r="D8" t="str" s="252">
+        <v>{"label": "マド／テラス", "group": "opening", "internal": true}</v>
+      </c>
+      <c r="E8" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F8" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B9" t="str" s="252">
+        <v>spec_sash_configuration</v>
+      </c>
+      <c r="C9" t="str" s="252">
+        <v>window_type</v>
+      </c>
+      <c r="D9" t="str" s="252">
+        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E9" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F9" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B10" t="str" s="252">
+        <v>spec_crescent_position</v>
+      </c>
+      <c r="C10" t="str" s="252">
+        <v>window_type</v>
+      </c>
+      <c r="D10" t="str" s="252">
+        <v>{"label": "クレセント位置", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E10" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F10" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B11" t="str" s="252">
+        <v>screen</v>
+      </c>
+      <c r="C11" t="str" s="252">
+        <v>spec_height_category,window_type</v>
+      </c>
+      <c r="D11" t="str" s="252">
+        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
+      </c>
+      <c r="E11" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F11" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B12" t="str" s="252">
+        <v>size_mode</v>
+      </c>
+      <c r="C12" t="str" s="252"/>
+      <c r="D12" t="str" s="252">
+        <v>{"label": "寸法の指定方法", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E12" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F12" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B13" t="str" s="252">
+        <v>custom_width</v>
+      </c>
+      <c r="C13" t="str" s="252">
+        <v>size_mode</v>
+      </c>
+      <c r="D13" t="str" s="252">
+        <v>{"label": "製品仕上がり幅 W（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E13" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F13" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B14" t="str" s="252">
+        <v>custom_height</v>
+      </c>
+      <c r="C14" t="str" s="252">
+        <v>size_mode</v>
+      </c>
+      <c r="D14" t="str" s="252">
+        <v>{"label": "製品仕上がり高さ H（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E14" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F14" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B15" t="str" s="252">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="C15" t="str" s="252"/>
+      <c r="D15" t="str" s="252">
+        <v>{"label": "本体外観色", "group": "finish", "internal": false}</v>
+      </c>
+      <c r="E15" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F15" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B16" t="str" s="252">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C16" t="str" s="252">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="D16" t="str" s="252">
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E16" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F16" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B17" t="str" s="252">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="C17" t="str" s="252"/>
+      <c r="D17" t="str" s="252">
+        <v>{"label": "本体内観色", "group": "finish", "internal": false}</v>
+      </c>
+      <c r="E17" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F17" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B18" t="str" s="252">
+        <v>interior_resin_cover_color</v>
+      </c>
+      <c r="C18" t="str" s="252">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="D18" t="str" s="252">
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E18" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F18" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B19" t="str" s="252">
+        <v>wooden_casing_color</v>
+      </c>
+      <c r="C19" t="str" s="252">
+        <v>options</v>
+      </c>
+      <c r="D19" t="str" s="252">
+        <v>{"label": "木製ケーシング色", "group": "part_detail", "internal": false}</v>
+      </c>
+      <c r="E19" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F19" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B20" t="str" s="252">
+        <v>options</v>
+      </c>
+      <c r="C20" t="str" s="252"/>
+      <c r="D20" t="str" s="252">
+        <v>{"label": "追加部材・オプション", "group": "options", "internal": false}</v>
+      </c>
+      <c r="E20" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F20" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B21" t="str" s="252">
+        <v>installation_method</v>
+      </c>
+      <c r="C21" t="str" s="252"/>
+      <c r="D21" t="str" s="252">
+        <v>{"label": "施工方法", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E21" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F21" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B22" t="str" s="252">
+        <v>installation_region</v>
+      </c>
+      <c r="C22" t="str" s="252"/>
+      <c r="D22" t="str" s="252">
+        <v>{"label": "設置地域", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E22" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F22" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B23" t="str" s="252">
+        <v>glass_category</v>
+      </c>
+      <c r="C23" t="str" s="252">
+        <v>spec_sash_configuration,window_type</v>
+      </c>
+      <c r="D23" t="str" s="252">
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E23" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F23" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B24" t="str" s="252">
+        <v>glass</v>
+      </c>
+      <c r="C24" t="str" s="252">
+        <v>glass_category,installation_region,window_type</v>
+      </c>
+      <c r="D24" t="str" s="252">
+        <v>{"label": "Low-E構成", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E24" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F24" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B25" t="str" s="252">
+        <v>glass_gas</v>
+      </c>
+      <c r="C25" t="str" s="252">
+        <v>glass_category,window_type</v>
+      </c>
+      <c r="D25" t="str" s="252">
+        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E25" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F25" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B26" t="str" s="252">
+        <v>glass_spacer</v>
+      </c>
+      <c r="C26" t="str" s="252">
+        <v>glass_category,glass_gas,window_type</v>
+      </c>
+      <c r="D26" t="str" s="252">
+        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E26" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F26" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B27" t="str" s="252">
+        <v>glass_function</v>
+      </c>
+      <c r="C27" t="str" s="252">
+        <v>glass_category,glass,window_type</v>
+      </c>
+      <c r="D27" t="str" s="252">
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E27" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F27" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B28" t="str" s="252">
+        <v>glass_appearance</v>
+      </c>
+      <c r="C28" t="str" s="252">
+        <v>glass,glass_function</v>
+      </c>
+      <c r="D28" t="str" s="252">
+        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E28" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F28" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B29" t="str" s="252">
+        <v>interior_cover_type</v>
+      </c>
+      <c r="C29" t="str" s="252"/>
+      <c r="D29" t="str" s="252">
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E29" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F29" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B30" t="str" s="252">
+        <v>exterior_cover_type</v>
+      </c>
+      <c r="C30" t="str" s="252">
+        <v>survey_cover_top,survey_cover_bottom,survey_cover_side</v>
+      </c>
+      <c r="D30" t="str" s="252">
+        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E30" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F30" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B31" t="str" s="252">
+        <v>survey_cover_top</v>
+      </c>
+      <c r="C31" t="str" s="252"/>
+      <c r="D31" t="str" s="252">
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E31" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F31" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B32" t="str" s="252">
+        <v>survey_cover_bottom</v>
+      </c>
+      <c r="C32" t="str" s="252"/>
+      <c r="D32" t="str" s="252">
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E32" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F32" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str" s="251">
+        <v>フロー</v>
+      </c>
+      <c r="B33" t="str" s="252">
+        <v>survey_cover_side</v>
+      </c>
+      <c r="C33" t="str" s="252"/>
+      <c r="D33" t="str" s="252">
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E33" t="str" s="253">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F33" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10300,388 +10938,356 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="68" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="243" t="str">
-        <x:v>01_入力フロー｜EWタイプ</x:v>
-      </x:c>
-      <x:c r="B1" s="243"/>
-      <x:c r="C1" s="243"/>
-      <x:c r="D1" s="243"/>
-      <x:c r="E1" s="243"/>
-    </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="248" t="str">
-        <x:v>順序</x:v>
-      </x:c>
-      <x:c r="B3" s="249" t="str">
-        <x:v>表示項目</x:v>
-      </x:c>
-      <x:c r="C3" s="249" t="str">
-        <x:v>データキー</x:v>
-      </x:c>
-      <x:c r="D3" s="249" t="str">
-        <x:v>候補/入力</x:v>
-      </x:c>
-      <x:c r="E3" s="250" t="str">
-        <x:v>制御</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="251" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="252" t="str">
-        <x:v>取替方式</x:v>
-      </x:c>
-      <x:c r="C4" s="252" t="str">
-        <x:v>installation_system_id</x:v>
-      </x:c>
-      <x:c r="D4" s="252" t="str">
-        <x:v>RPL_DIRECT</x:v>
-      </x:c>
-      <x:c r="E4" s="253" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="251" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="252" t="str">
-        <x:v>仕様区分</x:v>
-      </x:c>
-      <x:c r="C5" s="252" t="str">
-        <x:v>variation_id</x:v>
-      </x:c>
-      <x:c r="D5" s="252" t="str">
-        <x:v>RPL_EW</x:v>
-      </x:c>
-      <x:c r="E5" s="253" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="251" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="252" t="str">
-        <x:v>開口構成</x:v>
-      </x:c>
-      <x:c r="C6" s="252" t="str">
-        <x:v>opening_configuration</x:v>
-      </x:c>
-      <x:c r="D6" s="252" t="str">
-        <x:v>SINGLE</x:v>
-      </x:c>
-      <x:c r="E6" s="253" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="251" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="252" t="str">
-        <x:v>窓種</x:v>
-      </x:c>
-      <x:c r="C7" s="252" t="str">
-        <x:v>window_type_id</x:v>
-      </x:c>
-      <x:c r="D7" s="252" t="str">
-        <x:v>RPL_EW_SLD / 引違い窓</x:v>
-      </x:c>
-      <x:c r="E7" s="253" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="251" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="252" t="str">
-        <x:v>建数</x:v>
-      </x:c>
-      <x:c r="C8" s="252" t="str">
-        <x:v>panel_configuration</x:v>
-      </x:c>
-      <x:c r="D8" s="252" t="str">
-        <x:v>2枚建</x:v>
-      </x:c>
-      <x:c r="E8" s="253" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="251" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B9" s="252" t="str">
-        <x:v>高さ区分</x:v>
-      </x:c>
-      <x:c r="C9" s="252" t="str">
-        <x:v>height_category</x:v>
-      </x:c>
-      <x:c r="D9" s="252" t="str">
-        <x:v>マド / テラス</x:v>
-      </x:c>
-      <x:c r="E9" s="253" t="str">
-        <x:v>選択</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="251" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="252" t="str">
-        <x:v>障子仕様</x:v>
-      </x:c>
-      <x:c r="C10" s="252" t="str">
-        <x:v>sash_configuration</x:v>
-      </x:c>
-      <x:c r="D10" s="252" t="str">
-        <x:v>PG / TG / PGセレクト / TGセレクト</x:v>
-      </x:c>
-      <x:c r="E10" s="253" t="str">
-        <x:v>高さ区分とサイズで絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="251" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="252" t="str">
-        <x:v>採寸W/H</x:v>
-      </x:c>
-      <x:c r="C11" s="252" t="str">
-        <x:v>survey_w / survey_h</x:v>
-      </x:c>
-      <x:c r="D11" s="252" t="str">
-        <x:v>現場入力</x:v>
-      </x:c>
-      <x:c r="E11" s="253" t="str">
-        <x:v>3点採寸は現調レイヤー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="251" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B12" s="252" t="str">
-        <x:v>出来寸W/H</x:v>
-      </x:c>
-      <x:c r="C12" s="252" t="str">
-        <x:v>finished_w / finished_h</x:v>
-      </x:c>
-      <x:c r="D12" s="252" t="str">
-        <x:v>自動算出</x:v>
-      </x:c>
-      <x:c r="E12" s="253" t="str">
-        <x:v>WD=WS-10 / HD=HS-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="251" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B13" s="252" t="str">
-        <x:v>外観色</x:v>
-      </x:c>
-      <x:c r="C13" s="252" t="str">
-        <x:v>sash_exterior_color</x:v>
-      </x:c>
-      <x:c r="D13" s="252" t="str">
-        <x:v>4色</x:v>
-      </x:c>
-      <x:c r="E13" s="253" t="str">
-        <x:v>EW公式色のみ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="251" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B14" s="252" t="str">
-        <x:v>内観色</x:v>
-      </x:c>
-      <x:c r="C14" s="252" t="str">
-        <x:v>sash_interior_color</x:v>
-      </x:c>
-      <x:c r="D14" s="252" t="str">
-        <x:v>ピュアホワイト</x:v>
-      </x:c>
-      <x:c r="E14" s="253" t="str">
-        <x:v>固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="251" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B15" s="252" t="str">
-        <x:v>網戸</x:v>
-      </x:c>
-      <x:c r="C15" s="252" t="str">
-        <x:v>screen_type</x:v>
-      </x:c>
-      <x:c r="D15" s="252" t="str">
-        <x:v>なし / 引違い網戸</x:v>
-      </x:c>
-      <x:c r="E15" s="253" t="str">
-        <x:v>中桟軸なし</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="251" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B16" s="252" t="str">
-        <x:v>ネット</x:v>
-      </x:c>
-      <x:c r="C16" s="252" t="str">
-        <x:v>screen_mesh</x:v>
-      </x:c>
-      <x:c r="D16" s="252" t="str">
-        <x:v>標準/きれい/虫イヤ/ペット</x:v>
-      </x:c>
-      <x:c r="E16" s="253" t="str">
-        <x:v>網戸あり時のみ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="251" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B17" s="252" t="str">
-        <x:v>ガラス大分類</x:v>
-      </x:c>
-      <x:c r="C17" s="252" t="str">
-        <x:v>glass_category</x:v>
-      </x:c>
-      <x:c r="D17" s="252" t="str">
-        <x:v>LOW_E_DOUBLE / TRIPLE</x:v>
-      </x:c>
-      <x:c r="E17" s="253" t="str">
-        <x:v>障子仕様から自動連動</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="251" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B18" s="252" t="str">
-        <x:v>Low-E構成</x:v>
-      </x:c>
-      <x:c r="C18" s="252" t="str">
-        <x:v>glass_detail</x:v>
-      </x:c>
-      <x:c r="D18" s="252" t="str">
-        <x:v>公式構成</x:v>
-      </x:c>
-      <x:c r="E18" s="253" t="str">
-        <x:v>ガラス大分類・地域で絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="251" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B19" s="252" t="str">
-        <x:v>ガス</x:v>
-      </x:c>
-      <x:c r="C19" s="252" t="str">
-        <x:v>gas_type</x:v>
-      </x:c>
-      <x:c r="D19" s="252" t="str">
-        <x:v>アルゴン</x:v>
-      </x:c>
-      <x:c r="E19" s="253" t="str">
-        <x:v>AUTO_RESOLVED</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="251" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B20" s="252" t="str">
-        <x:v>スペーサー</x:v>
-      </x:c>
-      <x:c r="C20" s="252" t="str">
-        <x:v>spacer_type</x:v>
-      </x:c>
-      <x:c r="D20" s="252" t="str">
-        <x:v>樹脂</x:v>
-      </x:c>
-      <x:c r="E20" s="253" t="str">
-        <x:v>AUTO_RESOLVED</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="251" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B21" s="252" t="str">
-        <x:v>追加機能</x:v>
-      </x:c>
-      <x:c r="C21" s="252" t="str">
-        <x:v>glass_function</x:v>
-      </x:c>
-      <x:c r="D21" s="252" t="str">
-        <x:v>安全合わせ/フロスト等</x:v>
-      </x:c>
-      <x:c r="E21" s="253" t="str">
-        <x:v>公式条件で絞込</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="251" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B22" s="252" t="str">
-        <x:v>オプション</x:v>
-      </x:c>
-      <x:c r="C22" s="252" t="str">
-        <x:v>option_id</x:v>
-      </x:c>
-      <x:c r="D22" s="252" t="str">
-        <x:v>EW主要有償品</x:v>
-      </x:c>
-      <x:c r="E22" s="253" t="str">
-        <x:v>依存関係適用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="254" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B23" s="255" t="str">
-        <x:v>現調/施工判定</x:v>
-      </x:c>
-      <x:c r="C23" s="255" t="str">
-        <x:v>survey/installation_condition</x:v>
-      </x:c>
-      <x:c r="D23" s="255" t="str">
-        <x:v>別UI</x:v>
-      </x:c>
-      <x:c r="E23" s="256" t="str">
-        <x:v>商品選択とは分離</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="44" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="68" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" t="str" s="243">
+        <v>リプラス住宅用・グローバルセレクションフロー</v>
+      </c>
+      <c r="B1" s="243"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="243"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" t="str" s="248">
+        <v>順番</v>
+      </c>
+      <c r="B3" t="str" s="249">
+        <v>表示項目</v>
+      </c>
+      <c r="C3" t="str" s="249">
+        <v>データキー</v>
+      </c>
+      <c r="D3" t="str" s="249">
+        <v>候補/入力</v>
+      </c>
+      <c r="E3" t="str" s="250">
+        <v>制御方針</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="251">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str" s="252">
+        <v>商品・リプラス仕様</v>
+      </c>
+      <c r="C4" t="str" s="252">
+        <v>product / specification</v>
+      </c>
+      <c r="D4" t="str" s="252">
+        <v>リプラス住宅用 → 仕様</v>
+      </c>
+      <c r="E4" t="str" s="253">
+        <v>今回承認されたアプリ運用ルール</v>
+      </c>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="251">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str" s="252">
+        <v>設置・施工条件</v>
+      </c>
+      <c r="C5" t="str" s="252">
+        <v>context</v>
+      </c>
+      <c r="D5" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E5" t="str" s="253">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="251">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str" s="252">
+        <v>窓種・基本仕様</v>
+      </c>
+      <c r="C6" t="str" s="252">
+        <v>opening</v>
+      </c>
+      <c r="D6" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E6" t="str" s="253">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="251">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str" s="252">
+        <v>本体色</v>
+      </c>
+      <c r="C7" t="str" s="252">
+        <v>finish</v>
+      </c>
+      <c r="D7" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E7" t="str" s="253">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="251">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str" s="252">
+        <v>網戸</v>
+      </c>
+      <c r="C8" t="str" s="252">
+        <v>screen</v>
+      </c>
+      <c r="D8" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E8" t="str" s="253">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="251">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str" s="252">
+        <v>ガラス</v>
+      </c>
+      <c r="C9" t="str" s="252">
+        <v>glazing</v>
+      </c>
+      <c r="D9" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E9" t="str" s="253">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="251">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str" s="252">
+        <v>室内側の仕上げ・アングルカバー</v>
+      </c>
+      <c r="C10" t="str" s="252">
+        <v>interior_finish</v>
+      </c>
+      <c r="D10" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E10" t="str" s="253">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="251">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str" s="252">
+        <v>室外側の仕上げ・化粧カバー</v>
+      </c>
+      <c r="C11" t="str" s="252">
+        <v>exterior_finish</v>
+      </c>
+      <c r="D11" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E11" t="str" s="253">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="251">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str" s="252">
+        <v>新設サッシのオプション</v>
+      </c>
+      <c r="C12" t="str" s="252">
+        <v>native_options</v>
+      </c>
+      <c r="D12" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E12" t="str" s="253">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="251">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str" s="252">
+        <v>追加部材・オプション</v>
+      </c>
+      <c r="C13" t="str" s="252">
+        <v>options</v>
+      </c>
+      <c r="D13" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E13" t="str" s="253">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="251">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str" s="252">
+        <v>選択した部材の仕様</v>
+      </c>
+      <c r="C14" t="str" s="252">
+        <v>part_detail</v>
+      </c>
+      <c r="D14" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E14" t="str" s="253">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="251">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str" s="252">
+        <v>現場採寸・取付条件</v>
+      </c>
+      <c r="C15" t="str" s="252">
+        <v>survey</v>
+      </c>
+      <c r="D15" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E15" t="str" s="253">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="251">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str" s="252">
+        <v>製品寸法</v>
+      </c>
+      <c r="C16" t="str" s="252">
+        <v>size</v>
+      </c>
+      <c r="D16" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E16" t="str" s="253">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="251"/>
+      <c r="B17" s="252"/>
+      <c r="C17" s="252"/>
+      <c r="D17" s="252"/>
+      <c r="E17" s="253"/>
+      <c r="F17"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="251"/>
+      <c r="B18" s="252"/>
+      <c r="C18" s="252"/>
+      <c r="D18" s="252"/>
+      <c r="E18" s="253"/>
+      <c r="F18"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="251"/>
+      <c r="B19" s="252"/>
+      <c r="C19" s="252"/>
+      <c r="D19" s="252"/>
+      <c r="E19" s="253"/>
+      <c r="F19"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="251"/>
+      <c r="B20" s="252"/>
+      <c r="C20" s="252"/>
+      <c r="D20" s="252"/>
+      <c r="E20" s="253"/>
+      <c r="F20"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="251"/>
+      <c r="B21" s="252"/>
+      <c r="C21" s="252"/>
+      <c r="D21" s="252"/>
+      <c r="E21" s="253"/>
+      <c r="F21"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="251"/>
+      <c r="B22" s="252"/>
+      <c r="C22" s="252"/>
+      <c r="D22" s="252"/>
+      <c r="E22" s="253"/>
+      <c r="F22"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="254"/>
+      <c r="B23" s="255"/>
+      <c r="C23" s="255"/>
+      <c r="D23" s="255"/>
+      <c r="E23" s="256"/>
+      <c r="F23"/>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>

--- a/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
@@ -1505,7 +1505,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1525,7 +1525,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1543,7 +1543,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1563,7 +1563,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1583,7 +1583,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1623,7 +1623,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1643,7 +1643,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1663,7 +1663,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1681,7 +1681,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1701,7 +1701,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1721,7 +1721,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1739,7 +1739,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1759,7 +1759,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1777,7 +1777,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1797,7 +1797,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1817,7 +1817,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1835,7 +1835,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1853,7 +1853,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1871,7 +1871,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1891,7 +1891,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1931,7 +1931,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1951,7 +1951,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1971,7 +1971,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1991,7 +1991,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -2009,7 +2009,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -2029,7 +2029,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -2041,13 +2041,13 @@
       </c>
       <c r="C31" t="str" s="252"/>
       <c r="D31" t="str" s="252">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E31" t="str" s="253">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -2059,13 +2059,13 @@
       </c>
       <c r="C32" t="str" s="252"/>
       <c r="D32" t="str" s="252">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E32" t="str" s="253">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -2077,13 +2077,13 @@
       </c>
       <c r="C33" t="str" s="252"/>
       <c r="D33" t="str" s="252">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E33" t="str" s="253">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -11133,10 +11133,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="str" s="252">
-        <v>新設サッシのオプション</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C12" t="str" s="252">
-        <v>native_options</v>
+        <v>options</v>
       </c>
       <c r="D12" t="str" s="252">
         <v>選択・確認</v>
@@ -11151,10 +11151,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="str" s="252">
-        <v>追加部材・オプション</v>
+        <v>選択した部材の仕様</v>
       </c>
       <c r="C13" t="str" s="252">
-        <v>options</v>
+        <v>part_detail</v>
       </c>
       <c r="D13" t="str" s="252">
         <v>選択・確認</v>
@@ -11169,53 +11169,33 @@
         <v>11</v>
       </c>
       <c r="B14" t="str" s="252">
-        <v>選択した部材の仕様</v>
+        <v>製品寸法</v>
       </c>
       <c r="C14" t="str" s="252">
-        <v>part_detail</v>
+        <v>size</v>
       </c>
       <c r="D14" t="str" s="252">
         <v>選択・確認</v>
       </c>
       <c r="E14" t="str" s="253">
-        <v>対応する項目のみ表示</v>
+        <v>採寸後に再評価</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15">
-      <c r="A15" t="n" s="251">
-        <v>12</v>
-      </c>
-      <c r="B15" t="str" s="252">
-        <v>現場採寸・取付条件</v>
-      </c>
-      <c r="C15" t="str" s="252">
-        <v>survey</v>
-      </c>
-      <c r="D15" t="str" s="252">
-        <v>選択・確認</v>
-      </c>
-      <c r="E15" t="str" s="253">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A15" s="251"/>
+      <c r="B15" s="252"/>
+      <c r="C15" s="252"/>
+      <c r="D15" s="252"/>
+      <c r="E15" s="253"/>
       <c r="F15"/>
     </row>
     <row r="16">
-      <c r="A16" t="n" s="251">
-        <v>13</v>
-      </c>
-      <c r="B16" t="str" s="252">
-        <v>製品寸法</v>
-      </c>
-      <c r="C16" t="str" s="252">
-        <v>size</v>
-      </c>
-      <c r="D16" t="str" s="252">
-        <v>選択・確認</v>
-      </c>
-      <c r="E16" t="str" s="253">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A16" s="251"/>
+      <c r="B16" s="252"/>
+      <c r="C16" s="252"/>
+      <c r="D16" s="252"/>
+      <c r="E16" s="253"/>
       <c r="F16"/>
     </row>
     <row r="17">

--- a/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
@@ -1490,7 +1490,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str" s="251">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B3" t="str" s="252">
         <v>exterior_cover_color</v>
@@ -1505,12 +1505,12 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str" s="251">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B4" t="str" s="252">
         <v>interior_resin_cover_color</v>
@@ -1525,45 +1525,45 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str" s="251">
-        <v>フロー</v>
+        <v>NUMERIC_INPUT_PAIRS</v>
       </c>
       <c r="B5" t="str" s="252">
-        <v>window_type</v>
+        <v>dimension_basis</v>
       </c>
       <c r="C5" t="str" s="252"/>
       <c r="D5" t="str" s="252">
-        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
+        <v>{"basisField": "dimension_basis", "measuredBasis": "SURVEY", "finishedBasis": "FINISHED", "legacyBasis": "FINISHED", "evaluationAssignments": {"size_mode": "CUSTOM"}, "pairs": [{"measuredField": "survey_width", "finishedField": "custom_width", "offset": -10, "message": "公式換算：仕上がり寸法 = 採寸寸法 − 10mm。"}, {"measuredField": "survey_height", "finishedField": "custom_height", "offset": -10, "message": "公式換算：仕上がり寸法 = 採寸寸法 − 10mm。"}]}</v>
       </c>
       <c r="E5" t="str" s="253">
-        <v>UI_PRESENTATION</v>
+        <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str" s="251">
-        <v>フロー</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B6" t="str" s="252">
-        <v>frame_type</v>
+        <v>inner_fit_required_component</v>
       </c>
       <c r="C6" t="str" s="252">
-        <v>window_type</v>
+        <v>installation_method</v>
       </c>
       <c r="D6" t="str" s="252">
-        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
+        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "EW-OP-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "EW-OP-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。"}</v>
       </c>
       <c r="E6" t="str" s="253">
-        <v>UI_PRESENTATION</v>
+        <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1571,19 +1571,17 @@
         <v>フロー</v>
       </c>
       <c r="B7" t="str" s="252">
-        <v>spec_panel_configuration</v>
-      </c>
-      <c r="C7" t="str" s="252">
         <v>window_type</v>
       </c>
+      <c r="C7" t="str" s="252"/>
       <c r="D7" t="str" s="252">
-        <v>{"label": "建数", "group": "opening", "internal": false}</v>
+        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
       </c>
       <c r="E7" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1591,19 +1589,19 @@
         <v>フロー</v>
       </c>
       <c r="B8" t="str" s="252">
-        <v>spec_height_category</v>
+        <v>frame_type</v>
       </c>
       <c r="C8" t="str" s="252">
-        <v>window_type,custom_width,custom_height</v>
+        <v>window_type</v>
       </c>
       <c r="D8" t="str" s="252">
-        <v>{"label": "マド／テラス", "group": "opening", "internal": true}</v>
+        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
       </c>
       <c r="E8" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1611,19 +1609,19 @@
         <v>フロー</v>
       </c>
       <c r="B9" t="str" s="252">
-        <v>spec_sash_configuration</v>
+        <v>spec_panel_configuration</v>
       </c>
       <c r="C9" t="str" s="252">
         <v>window_type</v>
       </c>
       <c r="D9" t="str" s="252">
-        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
+        <v>{"label": "建数", "group": "opening", "internal": false}</v>
       </c>
       <c r="E9" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1631,19 +1629,19 @@
         <v>フロー</v>
       </c>
       <c r="B10" t="str" s="252">
-        <v>spec_crescent_position</v>
+        <v>spec_height_category</v>
       </c>
       <c r="C10" t="str" s="252">
-        <v>window_type</v>
+        <v>window_type,custom_width,custom_height</v>
       </c>
       <c r="D10" t="str" s="252">
-        <v>{"label": "クレセント位置", "group": "opening", "internal": false}</v>
+        <v>{"label": "マド／テラス", "group": "opening", "internal": true}</v>
       </c>
       <c r="E10" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1651,19 +1649,19 @@
         <v>フロー</v>
       </c>
       <c r="B11" t="str" s="252">
-        <v>screen</v>
+        <v>spec_sash_configuration</v>
       </c>
       <c r="C11" t="str" s="252">
-        <v>spec_height_category,window_type</v>
+        <v>window_type</v>
       </c>
       <c r="D11" t="str" s="252">
-        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
+        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
       </c>
       <c r="E11" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1671,17 +1669,19 @@
         <v>フロー</v>
       </c>
       <c r="B12" t="str" s="252">
-        <v>size_mode</v>
-      </c>
-      <c r="C12" t="str" s="252"/>
+        <v>spec_crescent_position</v>
+      </c>
+      <c r="C12" t="str" s="252">
+        <v>window_type</v>
+      </c>
       <c r="D12" t="str" s="252">
-        <v>{"label": "寸法の指定方法", "group": "size", "internal": false}</v>
+        <v>{"label": "クレセント位置", "group": "opening", "internal": false}</v>
       </c>
       <c r="E12" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1689,19 +1689,19 @@
         <v>フロー</v>
       </c>
       <c r="B13" t="str" s="252">
-        <v>custom_width</v>
+        <v>screen</v>
       </c>
       <c r="C13" t="str" s="252">
-        <v>size_mode</v>
+        <v>spec_height_category,window_type</v>
       </c>
       <c r="D13" t="str" s="252">
-        <v>{"label": "製品仕上がり幅 W（mm）", "group": "size", "internal": false}</v>
+        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
       </c>
       <c r="E13" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1709,19 +1709,17 @@
         <v>フロー</v>
       </c>
       <c r="B14" t="str" s="252">
-        <v>custom_height</v>
-      </c>
-      <c r="C14" t="str" s="252">
         <v>size_mode</v>
       </c>
+      <c r="C14" t="str" s="252"/>
       <c r="D14" t="str" s="252">
-        <v>{"label": "製品仕上がり高さ H（mm）", "group": "size", "internal": false}</v>
+        <v>{"label": "寸法の指定方法", "group": "size", "internal": true}</v>
       </c>
       <c r="E14" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1739,7 +1737,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1759,7 +1757,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1777,7 +1775,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1797,7 +1795,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1817,7 +1815,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1835,7 +1833,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1843,17 +1841,17 @@
         <v>フロー</v>
       </c>
       <c r="B21" t="str" s="252">
-        <v>installation_method</v>
+        <v>installation_region</v>
       </c>
       <c r="C21" t="str" s="252"/>
       <c r="D21" t="str" s="252">
-        <v>{"label": "施工方法", "group": "context", "internal": false}</v>
+        <v>{"label": "設置地域", "group": "context", "internal": false}</v>
       </c>
       <c r="E21" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1861,17 +1859,19 @@
         <v>フロー</v>
       </c>
       <c r="B22" t="str" s="252">
-        <v>installation_region</v>
-      </c>
-      <c r="C22" t="str" s="252"/>
+        <v>glass_category</v>
+      </c>
+      <c r="C22" t="str" s="252">
+        <v>spec_sash_configuration,window_type</v>
+      </c>
       <c r="D22" t="str" s="252">
-        <v>{"label": "設置地域", "group": "context", "internal": false}</v>
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E22" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1879,19 +1879,19 @@
         <v>フロー</v>
       </c>
       <c r="B23" t="str" s="252">
-        <v>glass_category</v>
+        <v>glass</v>
       </c>
       <c r="C23" t="str" s="252">
-        <v>spec_sash_configuration,window_type</v>
+        <v>glass_category,installation_region,window_type</v>
       </c>
       <c r="D23" t="str" s="252">
-        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+        <v>{"label": "Low-E構成", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E23" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1899,19 +1899,19 @@
         <v>フロー</v>
       </c>
       <c r="B24" t="str" s="252">
-        <v>glass</v>
+        <v>glass_gas</v>
       </c>
       <c r="C24" t="str" s="252">
-        <v>glass_category,installation_region,window_type</v>
+        <v>glass_category,window_type</v>
       </c>
       <c r="D24" t="str" s="252">
-        <v>{"label": "Low-E構成", "group": "glazing", "internal": false}</v>
+        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E24" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1919,19 +1919,19 @@
         <v>フロー</v>
       </c>
       <c r="B25" t="str" s="252">
-        <v>glass_gas</v>
+        <v>glass_spacer</v>
       </c>
       <c r="C25" t="str" s="252">
-        <v>glass_category,window_type</v>
+        <v>glass_category,glass_gas,window_type</v>
       </c>
       <c r="D25" t="str" s="252">
-        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
+        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E25" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1939,19 +1939,19 @@
         <v>フロー</v>
       </c>
       <c r="B26" t="str" s="252">
-        <v>glass_spacer</v>
+        <v>glass_function</v>
       </c>
       <c r="C26" t="str" s="252">
-        <v>glass_category,glass_gas,window_type</v>
+        <v>glass_category,glass,window_type</v>
       </c>
       <c r="D26" t="str" s="252">
-        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E26" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +1959,19 @@
         <v>フロー</v>
       </c>
       <c r="B27" t="str" s="252">
-        <v>glass_function</v>
+        <v>glass_appearance</v>
       </c>
       <c r="C27" t="str" s="252">
-        <v>glass_category,glass,window_type</v>
+        <v>glass,glass_function</v>
       </c>
       <c r="D27" t="str" s="252">
-        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E27" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1979,19 +1979,17 @@
         <v>フロー</v>
       </c>
       <c r="B28" t="str" s="252">
-        <v>glass_appearance</v>
-      </c>
-      <c r="C28" t="str" s="252">
-        <v>glass,glass_function</v>
-      </c>
+        <v>interior_cover_type</v>
+      </c>
+      <c r="C28" t="str" s="252"/>
       <c r="D28" t="str" s="252">
-        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
       </c>
       <c r="E28" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1999,17 +1997,19 @@
         <v>フロー</v>
       </c>
       <c r="B29" t="str" s="252">
-        <v>interior_cover_type</v>
-      </c>
-      <c r="C29" t="str" s="252"/>
+        <v>exterior_cover_type</v>
+      </c>
+      <c r="C29" t="str" s="252">
+        <v>survey_cover_top,survey_cover_bottom,survey_cover_side</v>
+      </c>
       <c r="D29" t="str" s="252">
-        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
       </c>
       <c r="E29" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -2017,19 +2017,19 @@
         <v>フロー</v>
       </c>
       <c r="B30" t="str" s="252">
-        <v>exterior_cover_type</v>
+        <v>installation_method</v>
       </c>
       <c r="C30" t="str" s="252">
-        <v>survey_cover_top,survey_cover_bottom,survey_cover_side</v>
+        <v>window_type</v>
       </c>
       <c r="D30" t="str" s="252">
-        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "内はめ仕様", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E30" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -2037,17 +2037,19 @@
         <v>フロー</v>
       </c>
       <c r="B31" t="str" s="252">
-        <v>survey_cover_top</v>
-      </c>
-      <c r="C31" t="str" s="252"/>
+        <v>inner_fit_required_component</v>
+      </c>
+      <c r="C31" t="str" s="252">
+        <v>installation_method</v>
+      </c>
       <c r="D31" t="str" s="252">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E31" t="str" s="253">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -2055,17 +2057,17 @@
         <v>フロー</v>
       </c>
       <c r="B32" t="str" s="252">
-        <v>survey_cover_bottom</v>
+        <v>dimension_basis</v>
       </c>
       <c r="C32" t="str" s="252"/>
       <c r="D32" t="str" s="252">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "入力する寸法", "group": "size", "internal": false}</v>
       </c>
       <c r="E32" t="str" s="253">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -2073,17 +2075,79 @@
         <v>フロー</v>
       </c>
       <c r="B33" t="str" s="252">
-        <v>survey_cover_side</v>
-      </c>
-      <c r="C33" t="str" s="252"/>
+        <v>survey_width</v>
+      </c>
+      <c r="C33" t="str" s="252">
+        <v>dimension_basis</v>
+      </c>
       <c r="D33" t="str" s="252">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "採寸幅 WS（mm）", "group": "size", "internal": false}</v>
       </c>
       <c r="E33" t="str" s="253">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B34" t="str">
+        <v>survey_height</v>
+      </c>
+      <c r="C34" t="str">
+        <v>dimension_basis</v>
+      </c>
+      <c r="D34" t="str">
+        <v>{"label": "採寸高さ HS（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E34" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F34" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B35" t="str">
+        <v>custom_width</v>
+      </c>
+      <c r="C35" t="str">
+        <v>dimension_basis</v>
+      </c>
+      <c r="D35" t="str">
+        <v>{"label": "製品仕上がり幅 WD（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E35" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F35" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>フロー</v>
+      </c>
+      <c r="B36" t="str">
+        <v>custom_height</v>
+      </c>
+      <c r="C36" t="str">
+        <v>dimension_basis</v>
+      </c>
+      <c r="D36" t="str">
+        <v>{"label": "製品仕上がり高さ HD（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E36" t="str">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F36" t="str">
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -2107,7 +2171,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="243" t="str">
+      <c r="A1" t="str" s="243">
         <v>90_Evidence｜EWタイプ 根拠管理</v>
       </c>
       <c r="B1" s="243"/>
@@ -2120,7 +2184,7 @@
       <c r="I1" s="243"/>
     </row>
     <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="244" t="str">
+      <c r="A2" t="str" s="244">
         <v>EW確定値はEW-EVを保持。2026業務用資料を最優先し、商品カタログ・現行Webを突合。</v>
       </c>
       <c r="B2" s="244"/>
@@ -2132,628 +2196,567 @@
       <c r="H2" s="244"/>
       <c r="I2" s="244"/>
     </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="248" t="str">
+      <c r="A4" t="str" s="248">
         <v>evidence_id</v>
       </c>
-      <c r="B4" s="249" t="str">
+      <c r="B4" t="str" s="249">
         <v>情報源種別</v>
       </c>
-      <c r="C4" s="249" t="str">
+      <c r="C4" t="str" s="249">
         <v>資料名</v>
       </c>
-      <c r="D4" s="249" t="str">
+      <c r="D4" t="str" s="249">
         <v>発行年月</v>
       </c>
-      <c r="E4" s="249" t="str">
+      <c r="E4" t="str" s="249">
         <v>ページ/箇所</v>
       </c>
-      <c r="F4" s="249" t="str">
+      <c r="F4" t="str" s="249">
         <v>URL</v>
       </c>
-      <c r="G4" s="249" t="str">
+      <c r="G4" t="str" s="249">
         <v>確認日</v>
       </c>
-      <c r="H4" s="249" t="str">
+      <c r="H4" t="str" s="249">
         <v>確度</v>
       </c>
-      <c r="I4" s="250" t="str">
+      <c r="I4" t="str" s="250">
         <v>根拠内容</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="251" t="str">
+      <c r="A5" t="str" s="251">
         <v>EW-EV-001</v>
       </c>
-      <c r="B5" s="252" t="str">
+      <c r="B5" t="str" s="252">
         <v>共通仕様</v>
       </c>
-      <c r="C5" s="252" t="str">
+      <c r="C5" t="str" s="252">
         <v>サッシ商品マスター共通仕様書_v0.1</v>
       </c>
-      <c r="D5" s="252" t="str">
+      <c r="D5" t="str" s="252">
         <v>2026-08-30更新</v>
       </c>
-      <c r="E5" s="252" t="str">
+      <c r="E5" t="str" s="252">
         <v>§31-34ほか</v>
       </c>
-      <c r="F5" s="252" t="str">
+      <c r="F5" t="str" s="252">
         <v>https://docs.google.com/document/d/1MfixkbV1cZ__DtBknEKsix_nnrXQqjc-LZtXUHwJv_A/edit</v>
       </c>
-      <c r="G5" s="252" t="str">
+      <c r="G5" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H5" s="252" t="str">
+      <c r="H5" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I5" s="253" t="str">
+      <c r="I5" t="str" s="253">
         <v>条件判定・耐風圧特殊案件・OP依存・UI非表示</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="251" t="str">
+      <c r="A6" t="str" s="251">
         <v>EW-EV-002</v>
       </c>
-      <c r="B6" s="252" t="str">
+      <c r="B6" t="str" s="252">
         <v>業務用資料集</v>
       </c>
-      <c r="C6" s="252" t="str">
+      <c r="C6" t="str" s="252">
         <v>リプラス・リプラスマンション用 取替窓 業務用資料集</v>
       </c>
-      <c r="D6" s="252" t="str">
+      <c r="D6" t="str" s="252">
         <v>2026-04</v>
       </c>
-      <c r="E6" s="252" t="str">
+      <c r="E6" t="str" s="252">
         <v>目次/居室仕様EWタイプ完成品価格表</v>
       </c>
-      <c r="F6" s="252" t="str">
+      <c r="F6" t="str" s="252">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G6" s="252" t="str">
+      <c r="G6" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H6" s="252" t="str">
+      <c r="H6" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I6" s="253" t="str">
+      <c r="I6" t="str" s="253">
         <v>EWタイプ商品体系、引違い窓・2枚建</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="251" t="str">
+      <c r="A7" t="str" s="251">
         <v>EW-EV-003</v>
       </c>
-      <c r="B7" s="252" t="str">
+      <c r="B7" t="str" s="252">
         <v>商品カタログ</v>
       </c>
-      <c r="C7" s="252" t="str">
+      <c r="C7" t="str" s="252">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D7" s="252" t="str">
+      <c r="D7" t="str" s="252">
         <v>2025-08</v>
       </c>
-      <c r="E7" s="252" t="str">
+      <c r="E7" t="str" s="252">
         <v>p.29/p.70ほか</v>
       </c>
-      <c r="F7" s="252" t="str">
+      <c r="F7" t="str" s="252">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G7" s="252" t="str">
+      <c r="G7" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H7" s="252" t="str">
+      <c r="H7" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I7" s="253" t="str">
+      <c r="I7" t="str" s="253">
         <v>EWタイプ商品体系・色・代表構成</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="251" t="str">
+      <c r="A8" t="str" s="251">
         <v>EW-EV-004</v>
       </c>
-      <c r="B8" s="252" t="str">
+      <c r="B8" t="str" s="252">
         <v>公式Web</v>
       </c>
-      <c r="C8" s="252" t="str">
+      <c r="C8" t="str" s="252">
         <v>LIXIL リプラス 居室仕様 EWタイプ</v>
       </c>
-      <c r="D8" s="252" t="str">
+      <c r="D8" t="str" s="252">
         <v>現行</v>
       </c>
-      <c r="E8" s="252" t="str">
+      <c r="E8" t="str" s="252">
         <v>品種/色/ガラス/網戸</v>
       </c>
-      <c r="F8" s="252" t="str">
+      <c r="F8" t="str" s="252">
         <v>https://www.lixil.co.jp/lineup/window/replus/variation/ew-type/</v>
       </c>
-      <c r="G8" s="252" t="str">
+      <c r="G8" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H8" s="252" t="str">
+      <c r="H8" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I8" s="253" t="str">
+      <c r="I8" t="str" s="253">
         <v>現行EW品種、色、ガラス、地域限定、網戸ネット</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="251" t="str">
+      <c r="A9" t="str" s="251">
         <v>EW-EV-005</v>
       </c>
-      <c r="B9" s="252" t="str">
+      <c r="B9" t="str" s="252">
         <v>業務用資料集</v>
       </c>
-      <c r="C9" s="252" t="str">
+      <c r="C9" t="str" s="252">
         <v>同上</v>
       </c>
-      <c r="D9" s="252" t="str">
+      <c r="D9" t="str" s="252">
         <v>2026-04</v>
       </c>
-      <c r="E9" s="252" t="str">
+      <c r="E9" t="str" s="252">
         <v>EWタイプ部材構成/完成品価格表</v>
       </c>
-      <c r="F9" s="252" t="str">
+      <c r="F9" t="str" s="252">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G9" s="252" t="str">
+      <c r="G9" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H9" s="252" t="str">
+      <c r="H9" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I9" s="253" t="str">
+      <c r="I9" t="str" s="253">
         <v>PG/TG/PGセレクト/TGセレクト、網戸、室内樹脂カバー、アルゴン＋樹脂</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="251" t="str">
+      <c r="A10" t="str" s="251">
         <v>EW-EV-006</v>
       </c>
-      <c r="B10" s="252" t="str">
+      <c r="B10" t="str" s="252">
         <v>業務用資料集</v>
       </c>
-      <c r="C10" s="252" t="str">
+      <c r="C10" t="str" s="252">
         <v>同上</v>
       </c>
-      <c r="D10" s="252" t="str">
+      <c r="D10" t="str" s="252">
         <v>2026-04</v>
       </c>
-      <c r="E10" s="252" t="str">
+      <c r="E10" t="str" s="252">
         <v>EWタイプマド/テラス価格表</v>
       </c>
-      <c r="F10" s="252" t="str">
+      <c r="F10" t="str" s="252">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G10" s="252" t="str">
+      <c r="G10" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H10" s="252" t="str">
+      <c r="H10" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I10" s="253" t="str">
+      <c r="I10" t="str" s="253">
         <v>2枚建のみ、セレクト障子・把手価格体系</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="251" t="str">
+      <c r="A11" t="str" s="251">
         <v>EW-EV-007</v>
       </c>
-      <c r="B11" s="252" t="str">
+      <c r="B11" t="str" s="252">
         <v>商品カタログ</v>
       </c>
-      <c r="C11" s="252" t="str">
+      <c r="C11" t="str" s="252">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D11" s="252" t="str">
+      <c r="D11" t="str" s="252">
         <v>2025-08</v>
       </c>
-      <c r="E11" s="252" t="str">
+      <c r="E11" t="str" s="252">
         <v>p.99</v>
       </c>
-      <c r="F11" s="252" t="str">
+      <c r="F11" t="str" s="252">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G11" s="252" t="str">
+      <c r="G11" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H11" s="252" t="str">
+      <c r="H11" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I11" s="253" t="str">
+      <c r="I11" t="str" s="253">
         <v>EW寸法特注範囲、WD/HD、境界式、内嵌め/ガラス完成品網掛け</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="251" t="str">
+      <c r="A12" t="str" s="251">
         <v>EW-EV-008</v>
       </c>
-      <c r="B12" s="252" t="str">
+      <c r="B12" t="str" s="252">
         <v>商品カタログ</v>
       </c>
-      <c r="C12" s="252" t="str">
+      <c r="C12" t="str" s="252">
         <v>同上</v>
       </c>
-      <c r="D12" s="252" t="str">
+      <c r="D12" t="str" s="252">
         <v>2025-08</v>
       </c>
-      <c r="E12" s="252" t="str">
+      <c r="E12" t="str" s="252">
         <v>p.52/p.60付近</v>
       </c>
-      <c r="F12" s="252" t="str">
+      <c r="F12" t="str" s="252">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G12" s="252" t="str">
+      <c r="G12" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H12" s="252" t="str">
+      <c r="H12" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I12" s="253" t="str">
+      <c r="I12" t="str" s="253">
         <v>EW Low-E複層/トリプル、Low-E色、アルゴン、樹脂スペーサー、追加機能</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="251" t="str">
+      <c r="A13" t="str" s="251">
         <v>EW-EV-009</v>
       </c>
-      <c r="B13" s="252" t="str">
+      <c r="B13" t="str" s="252">
         <v>商品カタログ</v>
       </c>
-      <c r="C13" s="252" t="str">
+      <c r="C13" t="str" s="252">
         <v>同上</v>
       </c>
-      <c r="D13" s="252" t="str">
+      <c r="D13" t="str" s="252">
         <v>2025-08</v>
       </c>
-      <c r="E13" s="252" t="str">
+      <c r="E13" t="str" s="252">
         <v>p.124</v>
       </c>
-      <c r="F13" s="252" t="str">
+      <c r="F13" t="str" s="252">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G13" s="252" t="str">
+      <c r="G13" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H13" s="252" t="str">
+      <c r="H13" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I13" s="253" t="str">
+      <c r="I13" t="str" s="253">
         <v>有償品取付可否、EW非適用OP、室内樹脂カバー/把手</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="251" t="str">
+      <c r="A14" t="str" s="251">
         <v>EW-EV-010</v>
       </c>
-      <c r="B14" s="252" t="str">
+      <c r="B14" t="str" s="252">
         <v>業務用資料集</v>
       </c>
-      <c r="C14" s="252" t="str">
+      <c r="C14" t="str" s="252">
         <v>同上</v>
       </c>
-      <c r="D14" s="252" t="str">
+      <c r="D14" t="str" s="252">
         <v>2026-04</v>
       </c>
-      <c r="E14" s="252" t="str">
+      <c r="E14" t="str" s="252">
         <v>EWタイプ有償品/セレクト障子</v>
       </c>
-      <c r="F14" s="252" t="str">
+      <c r="F14" t="str" s="252">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G14" s="252" t="str">
+      <c r="G14" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H14" s="252" t="str">
+      <c r="H14" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I14" s="253" t="str">
+      <c r="I14" t="str" s="253">
         <v>PGセレクト=大型把手、TGセレクト=アシスト把手</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="251" t="str">
+      <c r="A15" t="str" s="251">
         <v>EW-EV-011</v>
       </c>
-      <c r="B15" s="252" t="str">
+      <c r="B15" t="str" s="252">
         <v>商品カタログ</v>
       </c>
-      <c r="C15" s="252" t="str">
+      <c r="C15" t="str" s="252">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D15" s="252" t="str">
+      <c r="D15" t="str" s="252">
         <v>2025-08</v>
       </c>
-      <c r="E15" s="252" t="str">
+      <c r="E15" t="str" s="252">
         <v>p.242-243付近</v>
       </c>
-      <c r="F15" s="252" t="str">
+      <c r="F15" t="str" s="252">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G15" s="252" t="str">
+      <c r="G15" t="str" s="252">
         <v>2026-08-31</v>
       </c>
-      <c r="H15" s="252" t="str">
+      <c r="H15" t="str" s="252">
         <v>HIGH</v>
       </c>
-      <c r="I15" s="253" t="str">
+      <c r="I15" t="str" s="253">
         <v>EW現調/発注シート：3点採寸、見付、枠見込み、下枠、施工区分、室内樹脂カバーA/B/C、網戸</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="254" t="str">
+      <c r="A16" t="str" s="254">
         <v>EW-EV-012</v>
       </c>
-      <c r="B16" s="255" t="str">
+      <c r="B16" t="str" s="255">
         <v>商品カタログ</v>
       </c>
-      <c r="C16" s="255" t="str">
+      <c r="C16" t="str" s="255">
         <v>同上</v>
       </c>
-      <c r="D16" s="255" t="str">
+      <c r="D16" t="str" s="255">
         <v>2025-08</v>
       </c>
-      <c r="E16" s="255" t="str">
+      <c r="E16" t="str" s="255">
         <v>p.109付近</v>
       </c>
-      <c r="F16" s="255" t="str">
+      <c r="F16" t="str" s="255">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G16" s="255" t="str">
+      <c r="G16" t="str" s="255">
         <v>2026-08-31</v>
       </c>
-      <c r="H16" s="255" t="str">
+      <c r="H16" t="str" s="255">
         <v>HIGH</v>
       </c>
-      <c r="I16" s="256" t="str">
+      <c r="I16" t="str" s="256">
         <v>ガラス面積・戸車耐荷重・ガラス完成品製作範囲</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="187" t="inlineStr">
-        <is>
-          <t>DELTA-SPACER-EV-V4</t>
-        </is>
-      </c>
-      <c r="B17" s="188" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C17" s="188" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D17" s="188" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E17" s="188" t="inlineStr">
-        <is>
-          <t>PDF 52,104,116,120</t>
-        </is>
-      </c>
-      <c r="F17" s="188" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G17" s="188" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H17" s="188" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I17" s="189" t="inlineStr">
-        <is>
-          <t>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A17" t="str" s="187">
+        <v>DELTA-SPACER-EV-V4</v>
+      </c>
+      <c r="B17" t="str" s="188">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C17" t="str" s="188">
+        <v>IS9800</v>
+      </c>
+      <c r="D17" t="str" s="188">
+        <v>2026-10</v>
+      </c>
+      <c r="E17" t="str" s="188">
+        <v>PDF 52,104,116,120</v>
+      </c>
+      <c r="F17" t="str" s="188">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G17" t="str" s="188">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H17" t="str" s="188">
+        <v>HIGH</v>
+      </c>
+      <c r="I17" t="str" s="189">
+        <v>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>DELTA-CASING-EV-V4</t>
-        </is>
-      </c>
-      <c r="B18" s="36" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E18" s="36" t="inlineStr">
-        <is>
-          <t>PDF 51,115,119</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G18" s="36" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H18" s="36" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I18" s="37" t="inlineStr">
-        <is>
-          <t>UPDATE_WOODEN_CASING_COLOR_SCOPE / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A18" t="str" s="35">
+        <v>DELTA-CASING-EV-V4</v>
+      </c>
+      <c r="B18" t="str" s="36">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C18" t="str" s="36">
+        <v>IS9800</v>
+      </c>
+      <c r="D18" t="str" s="36">
+        <v>2026-10</v>
+      </c>
+      <c r="E18" t="str" s="36">
+        <v>PDF 51,115,119</v>
+      </c>
+      <c r="F18" t="str" s="36">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G18" t="str" s="36">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H18" t="str" s="36">
+        <v>HIGH</v>
+      </c>
+      <c r="I18" t="str" s="37">
+        <v>UPDATE_WOODEN_CASING_COLOR_SCOPE / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>DELTA-FILLER-EV-V4</t>
-        </is>
-      </c>
-      <c r="B19" s="36" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C19" s="36" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D19" s="36" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E19" s="36" t="inlineStr">
-        <is>
-          <t>PDF 51,115,119</t>
-        </is>
-      </c>
-      <c r="F19" s="36" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G19" s="36" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H19" s="36" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I19" s="37" t="inlineStr">
-        <is>
-          <t>UPDATE_FILLER_NAME_AND_VARIANTS / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A19" t="str" s="35">
+        <v>DELTA-FILLER-EV-V4</v>
+      </c>
+      <c r="B19" t="str" s="36">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C19" t="str" s="36">
+        <v>IS9800</v>
+      </c>
+      <c r="D19" t="str" s="36">
+        <v>2026-10</v>
+      </c>
+      <c r="E19" t="str" s="36">
+        <v>PDF 51,115,119</v>
+      </c>
+      <c r="F19" t="str" s="36">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G19" t="str" s="36">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H19" t="str" s="36">
+        <v>HIGH</v>
+      </c>
+      <c r="I19" t="str" s="37">
+        <v>UPDATE_FILLER_NAME_AND_VARIANTS / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t>DELTA-EW-CAPTION-EV-V4</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C20" s="39" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E20" s="39" t="inlineStr">
-        <is>
-          <t>PDF 42</t>
-        </is>
-      </c>
-      <c r="F20" s="39" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G20" s="39" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H20" s="39" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I20" s="40" t="inlineStr">
-        <is>
-          <t>CARRY_FORWARD_TECHNICAL_DIMENSIONS / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A20" t="str" s="38">
+        <v>DELTA-EW-CAPTION-EV-V4</v>
+      </c>
+      <c r="B20" t="str" s="39">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C20" t="str" s="39">
+        <v>IS9800</v>
+      </c>
+      <c r="D20" t="str" s="39">
+        <v>2026-10</v>
+      </c>
+      <c r="E20" t="str" s="39">
+        <v>PDF 42</v>
+      </c>
+      <c r="F20" t="str" s="39">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G20" t="str" s="39">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H20" t="str" s="39">
+        <v>HIGH</v>
+      </c>
+      <c r="I20" t="str" s="40">
+        <v>CARRY_FORWARD_TECHNICAL_DIMENSIONS / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-LEADTIME-EV-V4</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>PDF 235</t>
-        </is>
-      </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I21" s="28" t="inlineStr">
-        <is>
-          <t>SOURCE_NOTE_ONLY / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A21" t="str" s="28">
+        <v>DELTA-LEADTIME-EV-V4</v>
+      </c>
+      <c r="B21" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C21" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D21" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E21" t="str" s="28">
+        <v>PDF 235</v>
+      </c>
+      <c r="F21" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G21" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H21" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I21" t="str" s="28">
+        <v>SOURCE_NOTE_ONLY / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
+      <c r="A22" t="str" s="28">
+        <v>EV-DIMENSIONS-INNER-FIT-V11</v>
+      </c>
+      <c r="B22" t="str" s="28">
+        <v>公式商品カタログ</v>
+      </c>
+      <c r="C22" t="str" s="28">
+        <v>リプラス SN1200</v>
+      </c>
+      <c r="D22" t="str" s="28">
+        <v>2025-08</v>
+      </c>
+      <c r="E22" t="str" s="28">
+        <v>PDF252/254・231/233/247/249/251</v>
+      </c>
+      <c r="F22" t="str" s="28">
+        <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
+      </c>
+      <c r="G22" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H22" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I22" t="str" s="28">
+        <v>採寸/出来寸の相互換算と標準/内はめの施工仕様を共通Runtimeへ接続</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="28"/>
@@ -10998,7 +11001,7 @@
         <v>リプラス住宅用 → 仕様</v>
       </c>
       <c r="E4" t="str" s="253">
-        <v>今回承認されたアプリ運用ルール</v>
+        <v>アプリ運用ルール</v>
       </c>
       <c r="F4"/>
     </row>
@@ -11097,16 +11100,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="str" s="252">
-        <v>室内側の仕上げ・アングルカバー</v>
+        <v>内はめ仕様</v>
       </c>
       <c r="C10" t="str" s="252">
-        <v>interior_finish</v>
+        <v>inner_fit</v>
       </c>
       <c r="D10" t="str" s="252">
         <v>選択・確認</v>
       </c>
       <c r="E10" t="str" s="253">
-        <v>本体色に連動</v>
+        <v>ガラスの後で選択</v>
       </c>
       <c r="F10"/>
     </row>
@@ -11115,16 +11118,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="str" s="252">
-        <v>室外側の仕上げ・化粧カバー</v>
+        <v>室内側の仕上げ・アングルカバー</v>
       </c>
       <c r="C11" t="str" s="252">
-        <v>exterior_finish</v>
+        <v>interior_finish</v>
       </c>
       <c r="D11" t="str" s="252">
         <v>選択・確認</v>
       </c>
       <c r="E11" t="str" s="253">
-        <v>本体色に連動</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F11"/>
     </row>
@@ -11133,10 +11136,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="str" s="252">
-        <v>追加部材・オプション</v>
+        <v>室外側の仕上げ・化粧カバー</v>
       </c>
       <c r="C12" t="str" s="252">
-        <v>options</v>
+        <v>exterior_finish</v>
       </c>
       <c r="D12" t="str" s="252">
         <v>選択・確認</v>
@@ -11151,10 +11154,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="str" s="252">
-        <v>選択した部材の仕様</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C13" t="str" s="252">
-        <v>part_detail</v>
+        <v>options</v>
       </c>
       <c r="D13" t="str" s="252">
         <v>選択・確認</v>
@@ -11169,25 +11172,35 @@
         <v>11</v>
       </c>
       <c r="B14" t="str" s="252">
-        <v>製品寸法</v>
+        <v>選択した部材の仕様</v>
       </c>
       <c r="C14" t="str" s="252">
-        <v>size</v>
+        <v>part_detail</v>
       </c>
       <c r="D14" t="str" s="252">
         <v>選択・確認</v>
       </c>
       <c r="E14" t="str" s="253">
-        <v>採寸後に再評価</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15">
-      <c r="A15" s="251"/>
-      <c r="B15" s="252"/>
-      <c r="C15" s="252"/>
-      <c r="D15" s="252"/>
-      <c r="E15" s="253"/>
+      <c r="A15" t="n" s="251">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str" s="252">
+        <v>製品寸法</v>
+      </c>
+      <c r="C15" t="str" s="252">
+        <v>size</v>
+      </c>
+      <c r="D15" t="str" s="252">
+        <v>選択・確認</v>
+      </c>
+      <c r="E15" t="str" s="253">
+        <v>採寸と仕上がりを併記</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16">

--- a/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
@@ -1505,7 +1505,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1525,7 +1525,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1543,7 +1543,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1557,13 +1557,13 @@
         <v>installation_method</v>
       </c>
       <c r="D6" t="str" s="252">
-        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "EW-OP-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "EW-OP-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。"}</v>
+        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "EW-OP-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "EW-OP-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。", "resolvedNoticeVisibility": "INTERNAL_ONLY"}</v>
       </c>
       <c r="E6" t="str" s="253">
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1581,7 +1581,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1601,7 +1601,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1621,7 +1621,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1641,7 +1641,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1661,7 +1661,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1681,7 +1681,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1701,7 +1701,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1719,7 +1719,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1737,7 +1737,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1751,13 +1751,13 @@
         <v>sash_exterior_color</v>
       </c>
       <c r="D16" t="str" s="252">
-        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E16" t="str" s="253">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1775,7 +1775,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1789,13 +1789,13 @@
         <v>sash_interior_color</v>
       </c>
       <c r="D18" t="str" s="252">
-        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E18" t="str" s="253">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1815,7 +1815,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1833,7 +1833,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1851,7 +1851,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1871,7 +1871,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1891,7 +1891,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1931,7 +1931,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1951,7 +1951,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1971,7 +1971,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1989,7 +1989,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -2009,7 +2009,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -2029,7 +2029,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -2043,13 +2043,13 @@
         <v>installation_method</v>
       </c>
       <c r="D31" t="str" s="252">
-        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": false}</v>
+        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E31" t="str" s="253">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -2067,7 +2067,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -2087,7 +2087,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -2107,7 +2107,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -2127,7 +2127,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="36">
@@ -2147,7 +2147,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F36" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
   </sheetData>

--- a/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_EW.xlsx
@@ -1505,7 +1505,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1525,7 +1525,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1543,7 +1543,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1563,7 +1563,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1581,7 +1581,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1601,7 +1601,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1621,7 +1621,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1641,7 +1641,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1661,7 +1661,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1681,7 +1681,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1701,7 +1701,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1719,7 +1719,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1737,7 +1737,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1757,7 +1757,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1775,7 +1775,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1795,7 +1795,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1815,7 +1815,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1833,7 +1833,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1851,7 +1851,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1865,13 +1865,13 @@
         <v>spec_sash_configuration,window_type</v>
       </c>
       <c r="D22" t="str" s="252">
-        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false, "rank": 1}</v>
       </c>
       <c r="E22" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1882,16 +1882,16 @@
         <v>glass</v>
       </c>
       <c r="C23" t="str" s="252">
-        <v>glass_category,installation_region,window_type</v>
+        <v>glass_category,glass_appearance,installation_region,window_type</v>
       </c>
       <c r="D23" t="str" s="252">
-        <v>{"label": "Low-E構成", "group": "glazing", "internal": false}</v>
+        <v>{"label": "Low-E構成", "group": "glazing", "internal": false, "rank": 3}</v>
       </c>
       <c r="E23" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1931,7 +1931,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1942,16 +1942,16 @@
         <v>glass_function</v>
       </c>
       <c r="C26" t="str" s="252">
-        <v>glass_category,glass,window_type</v>
+        <v>glass_category,glass_appearance,glass,window_type</v>
       </c>
       <c r="D26" t="str" s="252">
-        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false, "rank": 4}</v>
       </c>
       <c r="E26" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1962,16 +1962,16 @@
         <v>glass_appearance</v>
       </c>
       <c r="C27" t="str" s="252">
-        <v>glass,glass_function</v>
+        <v>glass_category</v>
       </c>
       <c r="D27" t="str" s="252">
-        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス種", "group": "glazing", "internal": false, "rank": 2}</v>
       </c>
       <c r="E27" t="str" s="253">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1989,7 +1989,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -2009,7 +2009,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -2029,7 +2029,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -2049,7 +2049,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -2067,7 +2067,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -2087,7 +2087,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -2107,7 +2107,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -2127,7 +2127,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="36">
@@ -2147,7 +2147,67 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F36" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B37" t="str">
+        <v>glass_appearance</v>
+      </c>
+      <c r="C37" t="str">
+        <v>glass_category</v>
+      </c>
+      <c r="D37" t="str">
+        <v>{"key": "glass_appearance", "displayLabel": "ガラス種", "dataType": "ENUM", "displayOrder": 710, "required": false, "autoSelectSingle": false, "parentFields": ["glass_category"], "selector": {"glass_category": {"$exists": true}}, "choices": [{"value": "MILKY", "displayLabel": "乳白", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "CLEAR", "displayLabel": "透明", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 1}, {"value": "OBSCURE", "displayLabel": "型板", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "FROST", "displayLabel": "フロスト", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}]}</v>
+      </c>
+      <c r="E37" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F37" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B38" t="str">
+        <v>glass</v>
+      </c>
+      <c r="C38" t="str">
+        <v>glass_category,glass_appearance,installation_region,window_type</v>
+      </c>
+      <c r="D38" t="str">
+        <v>{"key": "glass", "displayLabel": "Low-E構成", "dataType": "ENUM", "displayOrder": 720, "choices": [{"value": "EW-D-CLEAR", "displayLabel": "クリア", "evidenceIds": ["EW-EV-004,008"], "selector": {"window_type": "RPL_EW_SLD", "glass_category": "EW-GL-DOUBLE"}, "metadata": {"manualCheck": true}}, {"value": "EW-D-GREEN", "displayLabel": "グリーン", "evidenceIds": ["EW-EV-004,008"], "selector": {"window_type": "RPL_EW_SLD", "glass_category": "EW-GL-DOUBLE"}, "metadata": {"manualCheck": true}}, {"value": "EW-D-GREEN-HS", "displayLabel": "グリーン（高遮熱仕様）", "evidenceIds": ["EW-EV-004,008"], "selector": {"window_type": "RPL_EW_SLD", "glass_category": "EW-GL-DOUBLE"}, "metadata": {"manualCheck": true}}, {"value": "EW-D-BRONZE", "displayLabel": "ブロンズ", "evidenceIds": ["EW-EV-004,008"], "selector": {"window_type": "RPL_EW_SLD", "glass_category": "EW-GL-DOUBLE", "installation_region": {"$in": ["北海道", "東北"]}}, "metadata": {"manualCheck": true}}, {"value": "EW-T-CC", "displayLabel": "クリア×クリア", "evidenceIds": ["EW-EV-004,008"], "selector": {"window_type": "RPL_EW_SLD", "glass_category": "EW-GL-TRIPLE"}, "metadata": {"manualCheck": true}}, {"value": "EW-T-GG", "displayLabel": "グリーン×グリーン", "evidenceIds": ["EW-EV-004,008"], "selector": {"window_type": "RPL_EW_SLD", "glass_category": "EW-GL-TRIPLE"}, "metadata": {"manualCheck": true}}, {"value": "EW-T-CG", "displayLabel": "クリア×グリーン", "evidenceIds": ["EW-EV-004,008"], "selector": {"window_type": "RPL_EW_SLD", "glass_category": "EW-GL-TRIPLE"}, "metadata": {"manualCheck": true}}, {"value": "EW-T-CB", "displayLabel": "クリア×ブロンズ", "evidenceIds": ["EW-EV-004,008"], "selector": {"window_type": "RPL_EW_SLD", "glass_category": "EW-GL-TRIPLE", "installation_region": {"$in": ["北海道", "東北"]}}, "metadata": {"manualCheck": true}}], "required": false, "autoSelectSingle": false, "parentFields": ["glass_category", "glass_appearance", "installation_region", "window_type"], "selector": {"glass_category": {"$exists": true}}}</v>
+      </c>
+      <c r="E38" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F38" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B39" t="str">
+        <v>glass_function</v>
+      </c>
+      <c r="C39" t="str">
+        <v>glass_category,glass_appearance,glass,window_type</v>
+      </c>
+      <c r="D39" t="str">
+        <v>{"key": "glass_function", "displayLabel": "ガラス追加機能", "dataType": "ENUM", "displayOrder": 730, "required": false, "autoSelectSingle": false, "parentFields": ["glass_category", "glass_appearance", "glass", "window_type"], "selector": {"glass": {"$exists": true}}, "choices": [{"value": "NONE", "displayLabel": "なし（標準）", "selector": {"all": [{"glass_category": "EW-GL-DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": false, "estimateConfirmationRequired": false}, "displayOrder": 1}, {"value": "SAFETY", "displayLabel": "安全合わせ", "selector": {"all": [{"glass_category": "EW-GL-DOUBLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "MILKY", "displayLabel": "安全合わせ乳白タイプ", "selector": {"all": [{"glass_category": "EW-GL-DOUBLE", "glass": {"$exists": true}}, {"glass_appearance": "MILKY"}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}, {"value": "NONE", "displayLabel": "なし（標準）", "selector": {"all": [{"glass_category": "EW-GL-TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": false, "estimateConfirmationRequired": false}, "displayOrder": 1}, {"value": "SAFETY", "displayLabel": "安全合わせ", "selector": {"all": [{"glass_category": "EW-GL-TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "MILKY", "displayLabel": "安全合わせ乳白タイプ", "selector": {"all": [{"glass_category": "EW-GL-TRIPLE", "glass": {"$exists": true}}, {"glass_appearance": "MILKY"}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}, {"value": "THIN", "displayLabel": "特殊薄板合わせ", "selector": {"all": [{"glass_category": "EW-GL-TRIPLE", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}]}</v>
+      </c>
+      <c r="E39" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F39" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
   </sheetData>
